--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Butterflies/Red-Admiral-Butterfly.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Butterflies/Red-Admiral-Butterfly.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
